--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,6 +926,1272 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125981805</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>737011</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7372093</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125981798</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91811</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1179</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gräddticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Perenniporia subacida</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>737156</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7372386</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125981811</v>
+      </c>
+      <c r="B6" t="n">
+        <v>82779</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>737019</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7372136</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125981812</v>
+      </c>
+      <c r="B7" t="n">
+        <v>82779</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>737094</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7372153</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125981803</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>737005</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7372171</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125981814</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>737121</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7372208</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125981807</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>737172</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7372383</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125981787</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>737060</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7372122</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppflog av tjäderhöna</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125981792</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>737091</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7372136</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125981804</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>737023</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7372136</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125981791</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>737003</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7372186</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125981793</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>737139</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7372284</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125981810</v>
+      </c>
+      <c r="B16" t="n">
+        <v>82779</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>737016</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7372145</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,32 +929,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125981805</v>
+        <v>125981798</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>91812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>737011</v>
+        <v>737156</v>
       </c>
       <c r="R4" t="n">
-        <v>7372093</v>
+        <v>7372386</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,32 +1026,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125981798</v>
+        <v>125981805</v>
       </c>
       <c r="B5" t="n">
-        <v>91811</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>737156</v>
+        <v>737011</v>
       </c>
       <c r="R5" t="n">
-        <v>7372386</v>
+        <v>7372093</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1126,7 +1126,7 @@
         <v>125981811</v>
       </c>
       <c r="B6" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>125981812</v>
       </c>
       <c r="B7" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125981803</v>
+        <v>125981806</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>737005</v>
+        <v>737119</v>
       </c>
       <c r="R8" t="n">
-        <v>7372171</v>
+        <v>7372343</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,32 +1414,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125981814</v>
+        <v>125981803</v>
       </c>
       <c r="B9" t="n">
-        <v>92509</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>737121</v>
+        <v>737005</v>
       </c>
       <c r="R9" t="n">
-        <v>7372208</v>
+        <v>7372171</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1511,32 +1511,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125981807</v>
+        <v>125981814</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>92510</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>737172</v>
+        <v>737121</v>
       </c>
       <c r="R10" t="n">
-        <v>7372383</v>
+        <v>7372208</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,32 +1608,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125981787</v>
+        <v>125981807</v>
       </c>
       <c r="B11" t="n">
-        <v>56843</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>737060</v>
+        <v>737172</v>
       </c>
       <c r="R11" t="n">
-        <v>7372122</v>
+        <v>7372383</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1679,11 +1679,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppflog av tjäderhöna</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,32 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125981792</v>
+        <v>125981787</v>
       </c>
       <c r="B12" t="n">
-        <v>57648</v>
+        <v>56843</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>737091</v>
+        <v>737060</v>
       </c>
       <c r="R12" t="n">
-        <v>7372136</v>
+        <v>7372122</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1781,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Uppflog av tjäderhöna</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125981804</v>
+        <v>125981792</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>737023</v>
+        <v>737091</v>
       </c>
       <c r="R13" t="n">
         <v>7372136</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125981791</v>
+        <v>125981804</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>737003</v>
+        <v>737023</v>
       </c>
       <c r="R14" t="n">
-        <v>7372186</v>
+        <v>7372136</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125981793</v>
+        <v>125981791</v>
       </c>
       <c r="B15" t="n">
         <v>57648</v>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>737139</v>
+        <v>737003</v>
       </c>
       <c r="R15" t="n">
-        <v>7372284</v>
+        <v>7372186</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2098,10 +2098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125981810</v>
+        <v>125981793</v>
       </c>
       <c r="B16" t="n">
-        <v>82779</v>
+        <v>57648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,21 +2109,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>737016</v>
+        <v>737139</v>
       </c>
       <c r="R16" t="n">
-        <v>7372145</v>
+        <v>7372284</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2192,6 +2192,103 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125981810</v>
+      </c>
+      <c r="B17" t="n">
+        <v>82780</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Björkberg Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>737016</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7372145</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -929,32 +929,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125981798</v>
+        <v>125981805</v>
       </c>
       <c r="B4" t="n">
-        <v>91812</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>737156</v>
+        <v>737011</v>
       </c>
       <c r="R4" t="n">
-        <v>7372386</v>
+        <v>7372093</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,32 +1026,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125981805</v>
+        <v>125981798</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>91815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>737011</v>
+        <v>737156</v>
       </c>
       <c r="R5" t="n">
-        <v>7372093</v>
+        <v>7372386</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125981806</v>
+        <v>125981803</v>
       </c>
       <c r="B8" t="n">
         <v>78968</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>737119</v>
+        <v>737005</v>
       </c>
       <c r="R8" t="n">
-        <v>7372343</v>
+        <v>7372171</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125981803</v>
+        <v>125981806</v>
       </c>
       <c r="B9" t="n">
         <v>78968</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>737005</v>
+        <v>737119</v>
       </c>
       <c r="R9" t="n">
-        <v>7372171</v>
+        <v>7372343</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1514,7 +1514,7 @@
         <v>125981814</v>
       </c>
       <c r="B10" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -929,32 +929,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125981805</v>
+        <v>125981798</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>91819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>737011</v>
+        <v>737156</v>
       </c>
       <c r="R4" t="n">
-        <v>7372093</v>
+        <v>7372386</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,32 +1026,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125981798</v>
+        <v>125981805</v>
       </c>
       <c r="B5" t="n">
-        <v>91815</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>737156</v>
+        <v>737011</v>
       </c>
       <c r="R5" t="n">
-        <v>7372386</v>
+        <v>7372093</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1126,7 +1126,7 @@
         <v>125981811</v>
       </c>
       <c r="B6" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>125981812</v>
       </c>
       <c r="B7" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125981803</v>
+        <v>125981806</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>737005</v>
+        <v>737119</v>
       </c>
       <c r="R8" t="n">
-        <v>7372171</v>
+        <v>7372343</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125981806</v>
+        <v>125981803</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>737119</v>
+        <v>737005</v>
       </c>
       <c r="R9" t="n">
-        <v>7372343</v>
+        <v>7372171</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1514,7 +1514,7 @@
         <v>125981814</v>
       </c>
       <c r="B10" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>125981807</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>125981804</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>125981810</v>
       </c>
       <c r="B17" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -929,32 +929,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125981798</v>
+        <v>125981805</v>
       </c>
       <c r="B4" t="n">
-        <v>91819</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>737156</v>
+        <v>737011</v>
       </c>
       <c r="R4" t="n">
-        <v>7372386</v>
+        <v>7372093</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,32 +1026,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125981805</v>
+        <v>125981798</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>91819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>737011</v>
+        <v>737156</v>
       </c>
       <c r="R5" t="n">
-        <v>7372093</v>
+        <v>7372386</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -929,32 +929,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125981805</v>
+        <v>125981798</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>91819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>737011</v>
+        <v>737156</v>
       </c>
       <c r="R4" t="n">
-        <v>7372093</v>
+        <v>7372386</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,32 +1026,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125981798</v>
+        <v>125981805</v>
       </c>
       <c r="B5" t="n">
-        <v>91819</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>737156</v>
+        <v>737011</v>
       </c>
       <c r="R5" t="n">
-        <v>7372386</v>
+        <v>7372093</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -929,32 +929,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125981798</v>
+        <v>125981805</v>
       </c>
       <c r="B4" t="n">
-        <v>91819</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>737156</v>
+        <v>737011</v>
       </c>
       <c r="R4" t="n">
-        <v>7372386</v>
+        <v>7372093</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,32 +1026,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125981805</v>
+        <v>125981798</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>91821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>737011</v>
+        <v>737156</v>
       </c>
       <c r="R5" t="n">
-        <v>7372093</v>
+        <v>7372386</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1126,7 +1126,7 @@
         <v>125981811</v>
       </c>
       <c r="B6" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>125981812</v>
       </c>
       <c r="B7" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>125981806</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>125981803</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>125981814</v>
       </c>
       <c r="B10" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>125981807</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>125981787</v>
       </c>
       <c r="B12" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>125981792</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>125981804</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>125981791</v>
       </c>
       <c r="B15" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>125981793</v>
       </c>
       <c r="B16" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>125981810</v>
       </c>
       <c r="B17" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -929,32 +929,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125981805</v>
+        <v>125981798</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>91821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>737011</v>
+        <v>737156</v>
       </c>
       <c r="R4" t="n">
-        <v>7372093</v>
+        <v>7372386</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,32 +1026,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125981798</v>
+        <v>125981805</v>
       </c>
       <c r="B5" t="n">
-        <v>91821</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>737156</v>
+        <v>737011</v>
       </c>
       <c r="R5" t="n">
-        <v>7372386</v>
+        <v>7372093</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>125981798</v>
       </c>
       <c r="B4" t="n">
-        <v>91821</v>
+        <v>91823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125981806</v>
+        <v>125981803</v>
       </c>
       <c r="B8" t="n">
         <v>78973</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>737119</v>
+        <v>737005</v>
       </c>
       <c r="R8" t="n">
-        <v>7372343</v>
+        <v>7372171</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125981803</v>
+        <v>125981806</v>
       </c>
       <c r="B9" t="n">
         <v>78973</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>737005</v>
+        <v>737119</v>
       </c>
       <c r="R9" t="n">
-        <v>7372171</v>
+        <v>7372343</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1514,7 +1514,7 @@
         <v>125981814</v>
       </c>
       <c r="B10" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>125981798</v>
       </c>
       <c r="B4" t="n">
-        <v>91823</v>
+        <v>91825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125981803</v>
+        <v>125981806</v>
       </c>
       <c r="B8" t="n">
         <v>78973</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>737005</v>
+        <v>737119</v>
       </c>
       <c r="R8" t="n">
-        <v>7372171</v>
+        <v>7372343</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125981806</v>
+        <v>125981803</v>
       </c>
       <c r="B9" t="n">
         <v>78973</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>737119</v>
+        <v>737005</v>
       </c>
       <c r="R9" t="n">
-        <v>7372343</v>
+        <v>7372171</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1514,7 +1514,7 @@
         <v>125981814</v>
       </c>
       <c r="B10" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>125981798</v>
       </c>
       <c r="B4" t="n">
-        <v>91825</v>
+        <v>91829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>125981805</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>125981811</v>
       </c>
       <c r="B6" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>125981812</v>
       </c>
       <c r="B7" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125981806</v>
+        <v>125981803</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>737119</v>
+        <v>737005</v>
       </c>
       <c r="R8" t="n">
-        <v>7372343</v>
+        <v>7372171</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125981803</v>
+        <v>125981806</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>737005</v>
+        <v>737119</v>
       </c>
       <c r="R9" t="n">
-        <v>7372171</v>
+        <v>7372343</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1514,7 +1514,7 @@
         <v>125981814</v>
       </c>
       <c r="B10" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>125981807</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>125981787</v>
       </c>
       <c r="B12" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>125981792</v>
       </c>
       <c r="B13" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>125981804</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>125981791</v>
       </c>
       <c r="B15" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>125981793</v>
       </c>
       <c r="B16" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>125981810</v>
       </c>
       <c r="B17" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125981803</v>
+        <v>125981806</v>
       </c>
       <c r="B8" t="n">
         <v>78977</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>737005</v>
+        <v>737119</v>
       </c>
       <c r="R8" t="n">
-        <v>7372171</v>
+        <v>7372343</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125981806</v>
+        <v>125981803</v>
       </c>
       <c r="B9" t="n">
         <v>78977</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>737119</v>
+        <v>737005</v>
       </c>
       <c r="R9" t="n">
-        <v>7372343</v>
+        <v>7372171</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -929,32 +929,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125981798</v>
+        <v>125981805</v>
       </c>
       <c r="B4" t="n">
-        <v>91829</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>737156</v>
+        <v>737011</v>
       </c>
       <c r="R4" t="n">
-        <v>7372386</v>
+        <v>7372093</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,32 +1026,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125981805</v>
+        <v>125981798</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>91829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>737011</v>
+        <v>737156</v>
       </c>
       <c r="R5" t="n">
-        <v>7372093</v>
+        <v>7372386</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>125981805</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>125981798</v>
       </c>
       <c r="B5" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>125981811</v>
       </c>
       <c r="B6" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>125981812</v>
       </c>
       <c r="B7" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>125981806</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>125981803</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>125981814</v>
       </c>
       <c r="B10" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>125981807</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>125981787</v>
       </c>
       <c r="B12" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>125981792</v>
       </c>
       <c r="B13" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>125981804</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>125981791</v>
       </c>
       <c r="B15" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>125981793</v>
       </c>
       <c r="B16" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>125981810</v>
       </c>
       <c r="B17" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -1708,7 +1708,7 @@
         <v>125981787</v>
       </c>
       <c r="B12" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -1708,7 +1708,7 @@
         <v>125981787</v>
       </c>
       <c r="B12" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -1708,7 +1708,7 @@
         <v>125981787</v>
       </c>
       <c r="B12" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -1708,7 +1708,7 @@
         <v>125981787</v>
       </c>
       <c r="B12" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -1708,7 +1708,7 @@
         <v>125981787</v>
       </c>
       <c r="B12" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -1708,7 +1708,7 @@
         <v>125981787</v>
       </c>
       <c r="B12" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -1708,7 +1708,7 @@
         <v>125981787</v>
       </c>
       <c r="B12" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27548-2025 artfynd.xlsx
+++ b/artfynd/A 27548-2025 artfynd.xlsx
@@ -1708,7 +1708,7 @@
         <v>125981787</v>
       </c>
       <c r="B12" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
